--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484839_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484839_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0056</v>
+        <v>8.9781</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7174</v>
+        <v>8.0867</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2882</v>
+        <v>0.8914</v>
       </c>
       <c r="G2" t="n">
         <v>3.6009</v>
@@ -610,13 +610,13 @@
         <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7745</v>
+        <v>1.7469</v>
       </c>
       <c r="T2" t="n">
-        <v>4.2559</v>
+        <v>1.6252</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.1218</v>
       </c>
       <c r="V2" t="n">
         <v>1.7433</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2279</v>
+        <v>2.0402</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5272</v>
+        <v>1.6834</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7007</v>
+        <v>0.3568</v>
       </c>
       <c r="G3" t="n">
         <v>0.09</v>
@@ -688,13 +688,13 @@
         <v>2.6418</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0546</v>
+        <v>0.8669</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5966</v>
+        <v>0.7528</v>
       </c>
       <c r="U3" t="n">
-        <v>0.458</v>
+        <v>0.1141</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4263</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6224</v>
+        <v>1.9036</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7079</v>
+        <v>4.3279</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-2.4242</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0669</v>
+        <v>2.3005</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8491</v>
+        <v>-1.5402</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9161</v>
+        <v>3.8407</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8097</v>
+        <v>3.5791</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3702</v>
+        <v>-0.3694</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4396</v>
+        <v>3.9485</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7428</v>
+        <v>-1.2786</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2193</v>
+        <v>-1.1708</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4765</v>
+        <v>-0.1078</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>-0.1887</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3292</v>
+        <v>-0.1029</v>
       </c>
       <c r="T4" t="n">
-        <v>0.238</v>
+        <v>0.3338</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0912</v>
+        <v>-0.4367</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6036</v>
+        <v>-1.9923</v>
       </c>
       <c r="W4" t="n">
         <v>0.6036</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.5959</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2699</v>
+        <v>1.3721</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8793</v>
+        <v>1.6692</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6094</v>
+        <v>-0.2971</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3005</v>
+        <v>1.0669</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5402</v>
+        <v>-0.8491</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8407</v>
+        <v>1.9161</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5791</v>
+        <v>1.8097</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3694</v>
+        <v>0.3702</v>
       </c>
       <c r="L5" t="n">
-        <v>3.9485</v>
+        <v>1.4396</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2786</v>
+        <v>-0.7428</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1708</v>
+        <v>-1.2193</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1078</v>
+        <v>0.4765</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6983</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7366</v>
+        <v>0.0789</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1147</v>
+        <v>0.1994</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6219</v>
+        <v>-0.1205</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9923</v>
+        <v>0.6036</v>
       </c>
       <c r="W5" t="n">
         <v>0.6036</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.5959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1519</v>
+        <v>1.2321</v>
       </c>
       <c r="E6" t="n">
-        <v>2.214</v>
+        <v>3.1883</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.062</v>
+        <v>-1.9562</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3854</v>
@@ -922,13 +922,13 @@
         <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.074</v>
+        <v>0.0062</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5879</v>
+        <v>0.3865</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4861</v>
+        <v>-0.3803</v>
       </c>
       <c r="V6" t="n">
         <v>0.4791</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. SOSA ASTACIO</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3407</v>
+        <v>0.0272</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1552</v>
+        <v>0.449</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1855</v>
+        <v>-0.4217</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1632</v>
+        <v>-1.5372</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2716</v>
+        <v>-0.3725</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1083</v>
+        <v>-1.1647</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0211</v>
+        <v>0.2238</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0211</v>
+        <v>0.7826</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.5588</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1843</v>
+        <v>-1.761</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2927</v>
+        <v>-1.1551</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1083</v>
+        <v>-0.6059</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1775</v>
+        <v>0.1871</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1764</v>
+        <v>0.1312</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0012</v>
+        <v>0.0559</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>E. SOSA ASTACIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.315</v>
+        <v>-0.1988</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6816</v>
+        <v>0.0396</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6334</v>
+        <v>-0.2384</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5372</v>
+        <v>-0.1632</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3725</v>
+        <v>-0.2716</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1647</v>
+        <v>0.1083</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2238</v>
+        <v>0.0211</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7826</v>
+        <v>0.0211</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5588</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.761</v>
+        <v>-0.1843</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1551</v>
+        <v>-0.2927</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6059</v>
+        <v>0.1083</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.887</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1551</v>
+        <v>-0.0356</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9994</v>
+        <v>0.0185</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1557</v>
+        <v>-0.0541</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3545</v>
+        <v>-1.7985</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4941</v>
+        <v>-0.188</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8486</v>
+        <v>-1.6105</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2743</v>
@@ -1156,13 +1156,13 @@
         <v>2.0757</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6101</v>
+        <v>0.1662</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6576</v>
+        <v>0.9756</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0475</v>
+        <v>-0.8094</v>
       </c>
       <c r="V9" t="n">
         <v>-2.6339</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8767</v>
+        <v>-5.8714</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.5566</v>
+        <v>-4.8158</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3201</v>
+        <v>-1.0556</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5288</v>
@@ -1234,13 +1234,13 @@
         <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.027</v>
+        <v>-0.0216</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5879</v>
+        <v>0.153</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4391</v>
+        <v>-0.1745</v>
       </c>
       <c r="V10" t="n">
         <v>-1.547</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.390799999999999</v>
+        <v>7.684600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>14.1465</v>
+        <v>14.4403</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.755599999999999</v>
+        <v>-6.7555</v>
       </c>
       <c r="G11" t="n">
         <v>4.1694</v>
@@ -1294,7 +1294,7 @@
         <v>6.058999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.6214</v>
+        <v>-9.621400000000001</v>
       </c>
       <c r="N11" t="n">
         <v>-11.465</v>
@@ -1312,10 +1312,10 @@
         <v>13.209</v>
       </c>
       <c r="S11" t="n">
-        <v>2.598199999999999</v>
+        <v>2.8921</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2818</v>
+        <v>4.576</v>
       </c>
       <c r="U11" t="n">
         <v>-1.6837</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ORTIN GOMEZ</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.2537</v>
+        <v>2.1178</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7867</v>
+        <v>3.4604</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.533</v>
+        <v>-1.3426</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9576</v>
+        <v>2.4056</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0268</v>
+        <v>0.9556</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0692</v>
+        <v>1.4501</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0754</v>
+        <v>3.046</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4088</v>
+        <v>1.1199</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6666</v>
+        <v>1.9261</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1179</v>
+        <v>-0.6403</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3821</v>
+        <v>-0.1643</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7358</v>
+        <v>-0.476</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3374</v>
+        <v>-0.5521</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.1127</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3738</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3622</v>
+        <v>-0.3018</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3622</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>A. ORTIN GOMEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9145</v>
+        <v>1.9433</v>
       </c>
       <c r="E13" t="n">
-        <v>3.363</v>
+        <v>3.3969</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4484</v>
+        <v>-1.4536</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4056</v>
+        <v>0.9576</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9556</v>
+        <v>1.0268</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4501</v>
+        <v>-0.0692</v>
       </c>
       <c r="J13" t="n">
-        <v>3.046</v>
+        <v>3.0754</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1199</v>
+        <v>2.4088</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9261</v>
+        <v>0.6666</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6403</v>
+        <v>-2.1179</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1643</v>
+        <v>-1.3821</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.476</v>
+        <v>-0.7358</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7554</v>
+        <v>0.027</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0152</v>
+        <v>0.3215</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7706</v>
+        <v>-0.2945</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3018</v>
+        <v>-0.3622</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6036</v>
+        <v>-0.3622</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. GALVEZ ARROYO</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6754</v>
+        <v>0.971</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6707</v>
+        <v>4.2641</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0047</v>
+        <v>-3.2931</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8895999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5956</v>
+        <v>3.8159</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4852</v>
+        <v>-3.8151</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0978</v>
+        <v>2.8889</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2154</v>
+        <v>5.3623</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1176</v>
+        <v>-2.4734</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9874000000000001</v>
+        <v>-2.8881</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6198</v>
+        <v>-1.5464</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3676</v>
+        <v>-1.3417</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9435</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3803</v>
+        <v>-0.7617</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6112</v>
+        <v>0.1682</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2309</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1282</v>
+        <v>2.1093</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7922</v>
+        <v>3.094</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.664</v>
+        <v>-0.9848</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>V. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2625</v>
+        <v>0.5952</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5821</v>
+        <v>0.6964</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3196</v>
+        <v>-0.1012</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0008</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8159</v>
+        <v>0.5956</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.8151</v>
+        <v>-1.4852</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8889</v>
+        <v>0.0978</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3623</v>
+        <v>1.2154</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.4734</v>
+        <v>-1.1176</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8881</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5464</v>
+        <v>-0.6198</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3417</v>
+        <v>-0.3676</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3774</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4702</v>
+        <v>0.3001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5139</v>
+        <v>0.6369</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9563</v>
+        <v>-0.3367</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1093</v>
+        <v>2.1282</v>
       </c>
       <c r="W15" t="n">
-        <v>3.094</v>
+        <v>2.7922</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9848</v>
+        <v>-0.664</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6973</v>
+        <v>-0.7947</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2316</v>
+        <v>2.1341</v>
       </c>
       <c r="F16" t="n">
         <v>-2.9289</v>
@@ -1702,10 +1702,10 @@
         <v>0.3774</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5661</v>
+        <v>-0.6635</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1793</v>
+        <v>0.0818</v>
       </c>
       <c r="U16" t="n">
         <v>-0.7454</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.0484</v>
+        <v>-2.9413</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.3225</v>
+        <v>-3.0301</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2741</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-2.6635</v>
@@ -1780,13 +1780,13 @@
         <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2416</v>
+        <v>0.3487</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0029</v>
+        <v>0.2952</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2387</v>
+        <v>0.0535</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0604</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6026</v>
+        <v>-3.5232</v>
       </c>
       <c r="E18" t="n">
         <v>-1.7236</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.879</v>
+        <v>-1.7996</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2663</v>
@@ -1858,13 +1858,13 @@
         <v>0.7548</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5967</v>
+        <v>-0.5173</v>
       </c>
       <c r="T18" t="n">
         <v>0.1328</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7295</v>
+        <v>-0.6501</v>
       </c>
       <c r="V18" t="n">
         <v>-0.664</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.1486</v>
+        <v>-5.7589</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8323</v>
+        <v>-2.4426</v>
       </c>
       <c r="F19" t="n">
         <v>-3.3163</v>
@@ -1936,10 +1936,10 @@
         <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1692</v>
+        <v>-0.7795</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4551</v>
+        <v>-0.0653</v>
       </c>
       <c r="U19" t="n">
         <v>-0.7141</v>
@@ -1972,7 +1972,7 @@
         <v>-7.3908</v>
       </c>
       <c r="E20" t="n">
-        <v>6.755699999999999</v>
+        <v>6.7556</v>
       </c>
       <c r="F20" t="n">
         <v>-14.1464</v>
@@ -2017,10 +2017,10 @@
         <v>-2.5983</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6836</v>
+        <v>1.6838</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.2819</v>
+        <v>-4.282</v>
       </c>
       <c r="V20" t="n">
         <v>3.1509</v>
